--- a/BWI/bestwine_output/bestwine_India.xlsx
+++ b/BWI/bestwine_output/bestwine_India.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA111"/>
+  <dimension ref="A1:AA113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12940,6 +12940,204 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Pegs India Company</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Pegs India Company</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>96109</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>72, Ground Floor, 15th Cross, Dr Puneeth Rajkumar Rd, 3rd Phase, J. P. Nagar</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>560078</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://pegsindia.com</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>admin@pegsindia.com</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>29AAZFP0193J1ZF</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pegs.houseofbooze/</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pegs.houseofbooze/</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr"/>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Beewin Beverages</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Beewin Beverages</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>55027</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Delhi, South West Delhi</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>349, S.m. Pur,near Igi Airport</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>110061</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beewinbev.com</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>info@beewinbev.com</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>+91 11 3561 4454</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>07AAZFB5605K1ZY</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beewin-beverages/</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>Vikash Kumar</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Manager</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vikash-kumar-3b528a291/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_India.xlsx
+++ b/BWI/bestwine_output/bestwine_India.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA113"/>
+  <dimension ref="A1:AA114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13138,6 +13138,87 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Lacave Fine Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Lacave Fine Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>58260</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Delhi, South Delhi</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>F-19, 20, 1st Floor, Select City Walk,  Saket District Centre, District Centre,  Sector 6, Pushp Vihar</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>110017</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://lacave.in</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>hello@lacave.in</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>+91 11 4654 4210</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacaveindia/</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacaveindia/</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr"/>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_India.xlsx
+++ b/BWI/bestwine_output/bestwine_India.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA114"/>
+  <dimension ref="A1:AA115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13219,6 +13219,91 @@
       <c r="Z114" s="2" t="inlineStr"/>
       <c r="AA114" s="2" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Hamsa Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Hamsa Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>118001</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Karnataka, Bangalore Division, Bengaluru Urban</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>325 12th Cross Road</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>560017</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://hamsaimportexport.com</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>admin@hamsaimportexport.com</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr"/>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>Ayyava Guna</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Ceo</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
